--- a/tame_output/MOZAIC/bt/btc_vs_alt_20230723.xlsx
+++ b/tame_output/MOZAIC/bt/btc_vs_alt_20230723.xlsx
@@ -52690,19 +52690,19 @@
         <v>1.628910960935361</v>
       </c>
       <c r="D2010" t="n">
-        <v>1.515547737385861</v>
+        <v>1.518426993447729</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.572229349160611</v>
+        <v>1.573668977191545</v>
       </c>
       <c r="F2010" t="n">
         <v>4.838309193352922</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.79296390393312</v>
+        <v>4.794115606357867</v>
       </c>
       <c r="H2010" t="n">
-        <v>4.815636548643011</v>
+        <v>4.816212399855384</v>
       </c>
     </row>
     <row r="2011">
@@ -52713,22 +52713,22 @@
         <v>4.191742345714202</v>
       </c>
       <c r="C2011" t="n">
-        <v>1.621906489069275</v>
+        <v>1.620402366596147</v>
       </c>
       <c r="D2011" t="n">
-        <v>1.509408693417485</v>
+        <v>1.512855187219056</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.56565759124338</v>
+        <v>1.566628776907601</v>
       </c>
       <c r="F2011" t="n">
-        <v>4.840504941341921</v>
+        <v>4.83990329235267</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.795505823081203</v>
+        <v>4.796884420601831</v>
       </c>
       <c r="H2011" t="n">
-        <v>4.818005382211552</v>
+        <v>4.81839385647724</v>
       </c>
     </row>
     <row r="2012">
@@ -52739,22 +52739,22 @@
         <v>4.1736787626571</v>
       </c>
       <c r="C2012" t="n">
-        <v>1.63008700856969</v>
+        <v>1.631377146292433</v>
       </c>
       <c r="D2012" t="n">
-        <v>1.518288098543662</v>
+        <v>1.522303684252304</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.574187553556676</v>
+        <v>1.576840415272369</v>
       </c>
       <c r="F2012" t="n">
-        <v>4.825713566084985</v>
+        <v>4.826229621174082</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.780994002074571</v>
+        <v>4.782600236358029</v>
       </c>
       <c r="H2012" t="n">
-        <v>4.803353784079768</v>
+        <v>4.804414928766045</v>
       </c>
     </row>
     <row r="2013">
@@ -52765,22 +52765,22 @@
         <v>4.155481419350962</v>
       </c>
       <c r="C2013" t="n">
-        <v>1.624218438856666</v>
+        <v>1.625205740375742</v>
       </c>
       <c r="D2013" t="n">
-        <v>1.515311323688657</v>
+        <v>1.51910037776473</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.569764881272661</v>
+        <v>1.572153059070236</v>
       </c>
       <c r="F2013" t="n">
-        <v>4.805168794893637</v>
+        <v>4.805563715501267</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.761605948826431</v>
+        <v>4.763121570456861</v>
       </c>
       <c r="H2013" t="n">
-        <v>4.783387371860024</v>
+        <v>4.784342642979054</v>
       </c>
     </row>
     <row r="2014">
@@ -52791,22 +52791,22 @@
         <v>4.146824167407236</v>
       </c>
       <c r="C2014" t="n">
-        <v>1.631345348937861</v>
+        <v>1.6355808814674</v>
       </c>
       <c r="D2014" t="n">
-        <v>1.526349789770667</v>
+        <v>1.530664619195981</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.578847569354264</v>
+        <v>1.58312275033169</v>
       </c>
       <c r="F2014" t="n">
-        <v>4.79936230698239</v>
+        <v>4.801056519994205</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.75736408331551</v>
+        <v>4.759090015085636</v>
       </c>
       <c r="H2014" t="n">
-        <v>4.778363195148939</v>
+        <v>4.78007326753991</v>
       </c>
     </row>
     <row r="2015">
@@ -52817,22 +52817,22 @@
         <v>4.134426248999913</v>
       </c>
       <c r="C2015" t="n">
-        <v>1.624747148511763</v>
+        <v>1.630144200439621</v>
       </c>
       <c r="D2015" t="n">
-        <v>1.525176071545981</v>
+        <v>1.530219857338158</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.574961610028872</v>
+        <v>1.580182028888889</v>
       </c>
       <c r="F2015" t="n">
-        <v>4.784325108404627</v>
+        <v>4.78648392917577</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.744496677618312</v>
+        <v>4.746514191935184</v>
       </c>
       <c r="H2015" t="n">
-        <v>4.764410893011459</v>
+        <v>4.766499060555466</v>
       </c>
     </row>
     <row r="2016">
@@ -52843,22 +52843,22 @@
         <v>4.154885080289795</v>
       </c>
       <c r="C2016" t="n">
-        <v>1.618743008175947</v>
+        <v>1.624940803301757</v>
       </c>
       <c r="D2016" t="n">
-        <v>1.520490349598126</v>
+        <v>1.525142251751433</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.569616678887037</v>
+        <v>1.575041527526595</v>
       </c>
       <c r="F2016" t="n">
-        <v>4.802382283560183</v>
+        <v>4.804861401610506</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.763081220129052</v>
+        <v>4.764941980990375</v>
       </c>
       <c r="H2016" t="n">
-        <v>4.782731751844607</v>
+        <v>4.78490169130043</v>
       </c>
     </row>
     <row r="2017">
@@ -52869,22 +52869,22 @@
         <v>4.145310928803405</v>
       </c>
       <c r="C2017" t="n">
-        <v>1.612513147465642</v>
+        <v>1.615348572983637</v>
       </c>
       <c r="D2017" t="n">
-        <v>1.513870599629186</v>
+        <v>1.516924005752613</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.563191873547414</v>
+        <v>1.566136289368125</v>
       </c>
       <c r="F2017" t="n">
-        <v>4.790316187789672</v>
+        <v>4.791450357996869</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.750859168655087</v>
+        <v>4.752080531104458</v>
       </c>
       <c r="H2017" t="n">
-        <v>4.770587678222369</v>
+        <v>4.771765444550653</v>
       </c>
     </row>
     <row r="2018">
@@ -52895,22 +52895,22 @@
         <v>4.133461272061444</v>
       </c>
       <c r="C2018" t="n">
-        <v>1.618009941576672</v>
+        <v>1.620845367094667</v>
       </c>
       <c r="D2018" t="n">
-        <v>1.511818211056303</v>
+        <v>1.514626663459292</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.564914076316487</v>
+        <v>1.567736015276979</v>
       </c>
       <c r="F2018" t="n">
-        <v>4.780665248692123</v>
+        <v>4.78179941889932</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.738188556483972</v>
+        <v>4.739311937445168</v>
       </c>
       <c r="H2018" t="n">
-        <v>4.759426902588037</v>
+        <v>4.760555678172233</v>
       </c>
     </row>
     <row r="2019">
@@ -52921,22 +52921,22 @@
         <v>4.136457215367947</v>
       </c>
       <c r="C2019" t="n">
-        <v>1.616526570328183</v>
+        <v>1.619361995846178</v>
       </c>
       <c r="D2019" t="n">
-        <v>1.514699225326681</v>
+        <v>1.519235674799341</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.565612897827432</v>
+        <v>1.569298835322759</v>
       </c>
       <c r="F2019" t="n">
-        <v>4.78306784349923</v>
+        <v>4.784202013706427</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.742336905498625</v>
+        <v>4.74415148528769</v>
       </c>
       <c r="H2019" t="n">
-        <v>4.762702374498917</v>
+        <v>4.764176749497048</v>
       </c>
     </row>
     <row r="2020">
@@ -52947,22 +52947,22 @@
         <v>4.145916630926916</v>
       </c>
       <c r="C2020" t="n">
-        <v>1.613817347891047</v>
+        <v>1.616652773409042</v>
       </c>
       <c r="D2020" t="n">
-        <v>1.516468388219437</v>
+        <v>1.521257593102917</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.565142868055242</v>
+        <v>1.56895518325598</v>
       </c>
       <c r="F2020" t="n">
-        <v>4.791443570083345</v>
+        <v>4.792577740290541</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.752503986214696</v>
+        <v>4.75441966816809</v>
       </c>
       <c r="H2020" t="n">
-        <v>4.77197377814901</v>
+        <v>4.773498704229304</v>
       </c>
     </row>
     <row r="2021">
@@ -52973,22 +52973,22 @@
         <v>4.141606803092691</v>
       </c>
       <c r="C2021" t="n">
-        <v>1.614719948726981</v>
+        <v>1.617555374244976</v>
       </c>
       <c r="D2021" t="n">
-        <v>1.527668255896632</v>
+        <v>1.532809919671265</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.571194102311806</v>
+        <v>1.57518264695812</v>
       </c>
       <c r="F2021" t="n">
-        <v>4.787494782583495</v>
+        <v>4.788628952790691</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.75267410545135</v>
+        <v>4.754730770961205</v>
       </c>
       <c r="H2021" t="n">
-        <v>4.770084444017411</v>
+        <v>4.771679861875936</v>
       </c>
     </row>
     <row r="2022">
@@ -52999,22 +52999,22 @@
         <v>4.154894226074353</v>
       </c>
       <c r="C2022" t="n">
-        <v>1.535817872658521</v>
+        <v>1.538653298176516</v>
       </c>
       <c r="D2022" t="n">
-        <v>1.469374035637011</v>
+        <v>1.470118687644395</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.502595954147766</v>
+        <v>1.504385992910456</v>
       </c>
       <c r="F2022" t="n">
-        <v>4.769221375137772</v>
+        <v>4.770355545344969</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.742643840329163</v>
+        <v>4.742941701132118</v>
       </c>
       <c r="H2022" t="n">
-        <v>4.755932607733456</v>
+        <v>4.756648623238531</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/bt/btc_vs_alt_20230723.xlsx
+++ b/tame_output/MOZAIC/bt/btc_vs_alt_20230723.xlsx
@@ -52690,19 +52690,19 @@
         <v>1.628910960935361</v>
       </c>
       <c r="D2010" t="n">
-        <v>1.518426993447729</v>
+        <v>1.515547737385861</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.573668977191545</v>
+        <v>1.572229349160611</v>
       </c>
       <c r="F2010" t="n">
         <v>4.838309193352922</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.794115606357867</v>
+        <v>4.79296390393312</v>
       </c>
       <c r="H2010" t="n">
-        <v>4.816212399855384</v>
+        <v>4.815636548643011</v>
       </c>
     </row>
     <row r="2011">
@@ -52713,22 +52713,22 @@
         <v>4.191742345714202</v>
       </c>
       <c r="C2011" t="n">
-        <v>1.620402366596147</v>
+        <v>1.621906489069275</v>
       </c>
       <c r="D2011" t="n">
-        <v>1.512855187219056</v>
+        <v>1.509408693417485</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.566628776907601</v>
+        <v>1.56565759124338</v>
       </c>
       <c r="F2011" t="n">
-        <v>4.83990329235267</v>
+        <v>4.840504941341921</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.796884420601831</v>
+        <v>4.795505823081203</v>
       </c>
       <c r="H2011" t="n">
-        <v>4.81839385647724</v>
+        <v>4.818005382211552</v>
       </c>
     </row>
     <row r="2012">
@@ -52739,22 +52739,22 @@
         <v>4.1736787626571</v>
       </c>
       <c r="C2012" t="n">
-        <v>1.631377146292433</v>
+        <v>1.63008700856969</v>
       </c>
       <c r="D2012" t="n">
-        <v>1.522303684252304</v>
+        <v>1.518288098543662</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.576840415272369</v>
+        <v>1.574187553556676</v>
       </c>
       <c r="F2012" t="n">
-        <v>4.826229621174082</v>
+        <v>4.825713566084985</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.782600236358029</v>
+        <v>4.780994002074571</v>
       </c>
       <c r="H2012" t="n">
-        <v>4.804414928766045</v>
+        <v>4.803353784079768</v>
       </c>
     </row>
     <row r="2013">
@@ -52765,22 +52765,22 @@
         <v>4.155481419350962</v>
       </c>
       <c r="C2013" t="n">
-        <v>1.625205740375742</v>
+        <v>1.624218438856666</v>
       </c>
       <c r="D2013" t="n">
-        <v>1.51910037776473</v>
+        <v>1.515311323688657</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.572153059070236</v>
+        <v>1.569764881272661</v>
       </c>
       <c r="F2013" t="n">
-        <v>4.805563715501267</v>
+        <v>4.805168794893637</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.763121570456861</v>
+        <v>4.761605948826431</v>
       </c>
       <c r="H2013" t="n">
-        <v>4.784342642979054</v>
+        <v>4.783387371860024</v>
       </c>
     </row>
     <row r="2014">
@@ -52791,22 +52791,22 @@
         <v>4.146824167407236</v>
       </c>
       <c r="C2014" t="n">
-        <v>1.6355808814674</v>
+        <v>1.631345348937861</v>
       </c>
       <c r="D2014" t="n">
-        <v>1.530664619195981</v>
+        <v>1.526349789770667</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.58312275033169</v>
+        <v>1.578847569354264</v>
       </c>
       <c r="F2014" t="n">
-        <v>4.801056519994205</v>
+        <v>4.79936230698239</v>
       </c>
       <c r="G2014" t="n">
-        <v>4.759090015085636</v>
+        <v>4.75736408331551</v>
       </c>
       <c r="H2014" t="n">
-        <v>4.78007326753991</v>
+        <v>4.778363195148939</v>
       </c>
     </row>
     <row r="2015">
@@ -52817,22 +52817,22 @@
         <v>4.134426248999913</v>
       </c>
       <c r="C2015" t="n">
-        <v>1.630144200439621</v>
+        <v>1.624747148511763</v>
       </c>
       <c r="D2015" t="n">
-        <v>1.530219857338158</v>
+        <v>1.525176071545981</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.580182028888889</v>
+        <v>1.574961610028872</v>
       </c>
       <c r="F2015" t="n">
-        <v>4.78648392917577</v>
+        <v>4.784325108404627</v>
       </c>
       <c r="G2015" t="n">
-        <v>4.746514191935184</v>
+        <v>4.744496677618312</v>
       </c>
       <c r="H2015" t="n">
-        <v>4.766499060555466</v>
+        <v>4.764410893011459</v>
       </c>
     </row>
     <row r="2016">
@@ -52843,22 +52843,22 @@
         <v>4.154885080289795</v>
       </c>
       <c r="C2016" t="n">
-        <v>1.624940803301757</v>
+        <v>1.618743008175947</v>
       </c>
       <c r="D2016" t="n">
-        <v>1.525142251751433</v>
+        <v>1.520490349598126</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.575041527526595</v>
+        <v>1.569616678887037</v>
       </c>
       <c r="F2016" t="n">
-        <v>4.804861401610506</v>
+        <v>4.802382283560183</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.764941980990375</v>
+        <v>4.763081220129052</v>
       </c>
       <c r="H2016" t="n">
-        <v>4.78490169130043</v>
+        <v>4.782731751844607</v>
       </c>
     </row>
     <row r="2017">
@@ -52869,22 +52869,22 @@
         <v>4.145310928803405</v>
       </c>
       <c r="C2017" t="n">
-        <v>1.615348572983637</v>
+        <v>1.612513147465642</v>
       </c>
       <c r="D2017" t="n">
-        <v>1.516924005752613</v>
+        <v>1.513870599629186</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.566136289368125</v>
+        <v>1.563191873547414</v>
       </c>
       <c r="F2017" t="n">
-        <v>4.791450357996869</v>
+        <v>4.790316187789672</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.752080531104458</v>
+        <v>4.750859168655087</v>
       </c>
       <c r="H2017" t="n">
-        <v>4.771765444550653</v>
+        <v>4.770587678222369</v>
       </c>
     </row>
     <row r="2018">
@@ -52895,22 +52895,22 @@
         <v>4.133461272061444</v>
       </c>
       <c r="C2018" t="n">
-        <v>1.620845367094667</v>
+        <v>1.618009941576672</v>
       </c>
       <c r="D2018" t="n">
-        <v>1.514626663459292</v>
+        <v>1.511818211056303</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.567736015276979</v>
+        <v>1.564914076316487</v>
       </c>
       <c r="F2018" t="n">
-        <v>4.78179941889932</v>
+        <v>4.780665248692123</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.739311937445168</v>
+        <v>4.738188556483972</v>
       </c>
       <c r="H2018" t="n">
-        <v>4.760555678172233</v>
+        <v>4.759426902588037</v>
       </c>
     </row>
     <row r="2019">
@@ -52921,22 +52921,22 @@
         <v>4.136457215367947</v>
       </c>
       <c r="C2019" t="n">
-        <v>1.619361995846178</v>
+        <v>1.616526570328183</v>
       </c>
       <c r="D2019" t="n">
-        <v>1.519235674799341</v>
+        <v>1.514699225326681</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.569298835322759</v>
+        <v>1.565612897827432</v>
       </c>
       <c r="F2019" t="n">
-        <v>4.784202013706427</v>
+        <v>4.78306784349923</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.74415148528769</v>
+        <v>4.742336905498625</v>
       </c>
       <c r="H2019" t="n">
-        <v>4.764176749497048</v>
+        <v>4.762702374498917</v>
       </c>
     </row>
     <row r="2020">
@@ -52947,22 +52947,22 @@
         <v>4.145916630926916</v>
       </c>
       <c r="C2020" t="n">
-        <v>1.616652773409042</v>
+        <v>1.613817347891047</v>
       </c>
       <c r="D2020" t="n">
-        <v>1.521257593102917</v>
+        <v>1.516468388219437</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.56895518325598</v>
+        <v>1.565142868055242</v>
       </c>
       <c r="F2020" t="n">
-        <v>4.792577740290541</v>
+        <v>4.791443570083345</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.75441966816809</v>
+        <v>4.752503986214696</v>
       </c>
       <c r="H2020" t="n">
-        <v>4.773498704229304</v>
+        <v>4.77197377814901</v>
       </c>
     </row>
     <row r="2021">
@@ -52973,22 +52973,22 @@
         <v>4.141606803092691</v>
       </c>
       <c r="C2021" t="n">
-        <v>1.617555374244976</v>
+        <v>1.614719948726981</v>
       </c>
       <c r="D2021" t="n">
-        <v>1.532809919671265</v>
+        <v>1.527668255896632</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.57518264695812</v>
+        <v>1.571194102311806</v>
       </c>
       <c r="F2021" t="n">
-        <v>4.788628952790691</v>
+        <v>4.787494782583495</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.754730770961205</v>
+        <v>4.75267410545135</v>
       </c>
       <c r="H2021" t="n">
-        <v>4.771679861875936</v>
+        <v>4.770084444017411</v>
       </c>
     </row>
     <row r="2022">
@@ -52999,22 +52999,22 @@
         <v>4.154894226074353</v>
       </c>
       <c r="C2022" t="n">
-        <v>1.538653298176516</v>
+        <v>1.535817872658521</v>
       </c>
       <c r="D2022" t="n">
-        <v>1.470118687644395</v>
+        <v>1.469374035637011</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.504385992910456</v>
+        <v>1.502595954147766</v>
       </c>
       <c r="F2022" t="n">
-        <v>4.770355545344969</v>
+        <v>4.769221375137772</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.742941701132118</v>
+        <v>4.742643840329163</v>
       </c>
       <c r="H2022" t="n">
-        <v>4.756648623238531</v>
+        <v>4.755932607733456</v>
       </c>
     </row>
   </sheetData>
